--- a/docs/From_Web.xlsx
+++ b/docs/From_Web.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uiChina_Web\China_Web_FE\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF5155D-75A0-454A-BB5D-1234E4FEB80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{DD2F049D-EF90-42F4-AD23-0C5B54E90754}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DD2F049D-EF90-42F4-AD23-0C5B54E90754}"/>
   </bookViews>
   <sheets>
     <sheet name="nội dung" sheetId="1" r:id="rId1"/>
@@ -416,7 +416,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -424,7 +424,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -432,13 +432,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -543,8 +543,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
-    <cellStyle name="Siêu kết nối" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -560,9 +560,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -600,7 +600,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -706,7 +706,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -848,7 +848,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -860,14 +860,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="100.4140625" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="22.08984375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="100.453125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -875,7 +875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -883,7 +883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -891,7 +891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -899,7 +899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -915,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -923,7 +923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="70" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
@@ -931,7 +931,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -939,7 +939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -947,13 +947,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="10"/>
     </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
@@ -961,7 +961,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -969,7 +969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -977,7 +977,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -985,7 +985,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>25</v>
       </c>
@@ -993,7 +993,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="42" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="280" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="290" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>32</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
@@ -1033,19 +1033,19 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="10"/>
     </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="10"/>
     </row>
-    <row r="24" spans="1:2" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="238" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>64</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>66</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>68</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="140" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="145" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>70</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="168" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>72</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>74</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="168" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>76</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>78</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>79</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>80</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>81</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>82</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>83</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="126" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>85</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>87</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>88</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>89</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>94</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>92</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>95</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>98</v>
       </c>
@@ -1240,12 +1240,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A55564-A53A-46A4-9EC4-39CE1F20245B}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>56</v>
       </c>
@@ -1494,7 +1494,7 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
     </row>
-    <row r="23" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
     </row>
-    <row r="25" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
         <v>99</v>
       </c>

--- a/docs/From_Web.xlsx
+++ b/docs/From_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\uiChina_Web\China_Web_FE\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF5155D-75A0-454A-BB5D-1234E4FEB80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B87A1FC-EAE9-41E6-A31F-A4219DE50B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DD2F049D-EF90-42F4-AD23-0C5B54E90754}"/>
   </bookViews>
